--- a/unified_service/database/tables/LLM.xlsx
+++ b/unified_service/database/tables/LLM.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="560">
   <si>
     <t>Страна</t>
   </si>
@@ -215,6 +215,9 @@
     <t>Сверхбыстрый инференс для диалогов и повседневных запросов</t>
   </si>
   <si>
+    <t>https://openai.com/ru-RU/index/gpt-5-3-instant/</t>
+  </si>
+  <si>
     <t>GPT-5.2 Pro</t>
   </si>
   <si>
@@ -530,6 +533,9 @@
     <t>Предшествующий флагман для комплексного анализа данных</t>
   </si>
   <si>
+    <t>https://deepmind.google/models/gemini/pro/</t>
+  </si>
+  <si>
     <t>Gemini 3 Flash</t>
   </si>
   <si>
@@ -1421,6 +1427,9 @@
     <t>Мультиязычная (с фокусом на русский)</t>
   </si>
   <si>
+    <t>https://ya.ru/ai/aliceai</t>
+  </si>
+  <si>
     <t>YandexGPT Pro 5.1</t>
   </si>
   <si>
@@ -1430,6 +1439,9 @@
     <t>Решение сложных бизнес-задач и нативная интеграция с Yandex Cloud</t>
   </si>
   <si>
+    <t>https://ya.ru/ai/gpt</t>
+  </si>
+  <si>
     <t>YandexGPT Pro 5</t>
   </si>
   <si>
@@ -1442,6 +1454,9 @@
     <t>Высокоточный поиск по корпоративным базам знаний и аналитика текстов</t>
   </si>
   <si>
+    <t>https://fichi.ai/yandexgpt-5</t>
+  </si>
+  <si>
     <t>Sber</t>
   </si>
   <si>
@@ -1487,6 +1502,9 @@
     <t>Глубокое понимание русского культурного контекста и работа с большими документами</t>
   </si>
   <si>
+    <t>https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-max</t>
+  </si>
+  <si>
     <t>GigaChat Pro</t>
   </si>
   <si>
@@ -1496,6 +1514,9 @@
     <t>Стабильная корпоративная автоматизация, аналитика и умный копирайтинг</t>
   </si>
   <si>
+    <t>https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-pro</t>
+  </si>
+  <si>
     <t>GigaChat Lite</t>
   </si>
   <si>
@@ -1511,6 +1532,9 @@
     <t>Только русский</t>
   </si>
   <si>
+    <t>https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-lite</t>
+  </si>
+  <si>
     <t>T-Bank</t>
   </si>
   <si>
@@ -1526,6 +1550,9 @@
     <t>Финансовая аналитика, автоматизация банкинга и парсинг логов</t>
   </si>
   <si>
+    <t>https://habr.com/ru/companies/tbank/articles/928956/</t>
+  </si>
+  <si>
     <t>Saiga</t>
   </si>
   <si>
@@ -1541,6 +1568,9 @@
     <t>Флагманские логические рассуждения и анализ текстов на русском языке</t>
   </si>
   <si>
+    <t>https://denciaopin.com/articles/saiga-family/</t>
+  </si>
+  <si>
     <t>Saiga Llama 4 8B</t>
   </si>
   <si>
@@ -1580,12 +1610,18 @@
     <t>Строгое следование сложным инструкциям на русском и анализ длинных текстов</t>
   </si>
   <si>
+    <t>https://huggingface.co/tripolskypetr/Vikhr-Nemo-12B-Instruct</t>
+  </si>
+  <si>
     <t>Vikhr-Llama-4-8B-Instruct</t>
   </si>
   <si>
     <t>Быстрый инференс для персональных ассистентов с качественным русским языком</t>
   </si>
   <si>
+    <t>https://huggingface.co/QuantFactory/Vikhr-Llama3.1-8B-Instruct-R-21-09-24-GGUF</t>
+  </si>
+  <si>
     <t>Канада</t>
   </si>
   <si>
@@ -1668,6 +1704,9 @@
   </si>
   <si>
     <t>Развертывание автономных агентов и эффективная работа с внешними базами</t>
+  </si>
+  <si>
+    <t>https://vlex-ai.io/ru/nejroseti-vlex-ai/command-r/</t>
   </si>
 </sst>
 </file>
@@ -1680,7 +1719,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1736,21 +1775,17 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF3C78D8"/>
+      <color theme="4"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="4"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1759,12 +1794,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="10"/>
-      <color rgb="FF0070C0"/>
+      <color theme="4"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2279,28 +2312,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2309,122 +2345,119 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2459,19 +2492,16 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2720,7 +2750,7 @@
         <strike val="0"/>
         <u val="none"/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="4"/>
       </font>
     </dxf>
     <dxf>
@@ -2765,7 +2795,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="LLM-style" pivot="0" count="4" xr9:uid="{17A6FD0E-E2CE-40BD-9DBA-2D7D53616654}">
+    <tableStyle name="LLM-style" pivot="0" count="4" xr9:uid="{3CA0785F-44B1-4915-9DE2-2999430285C8}">
       <tableStyleElement type="wholeTable" dxfId="17"/>
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
@@ -3068,7 +3098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="63.75" spans="1:14">
+    <row r="2" ht="51" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -3156,7 +3186,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" ht="63.75" spans="1:14">
+    <row r="4" ht="51" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -3200,7 +3230,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="89.25" spans="1:14">
+    <row r="5" ht="76.5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -3288,7 +3318,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" ht="63.75" spans="1:14">
+    <row r="7" ht="38.25" spans="1:14">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -3329,7 +3359,7 @@
         <v>25</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:14">
@@ -3340,19 +3370,19 @@
         <v>15</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>39</v>
@@ -3361,10 +3391,10 @@
         <v>1481</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>42</v>
@@ -3373,10 +3403,10 @@
         <v>25</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" ht="127.5" spans="1:14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" ht="114.75" spans="1:14">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -3384,19 +3414,19 @@
         <v>15</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>39</v>
@@ -3405,10 +3435,10 @@
         <v>1464</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>42</v>
@@ -3417,10 +3447,10 @@
         <v>25</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="63.75" spans="1:14">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" ht="51" spans="1:14">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -3428,19 +3458,19 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>39</v>
@@ -3449,10 +3479,10 @@
         <v>1455</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>42</v>
@@ -3461,7 +3491,7 @@
         <v>25</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="51" spans="1:14">
@@ -3472,13 +3502,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>37</v>
@@ -3493,10 +3523,10 @@
         <v>1479</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>42</v>
@@ -3505,24 +3535,24 @@
         <v>25</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" ht="114.75" spans="1:14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" ht="102" spans="1:14">
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>37</v>
@@ -3537,10 +3567,10 @@
         <v>1504</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>42</v>
@@ -3549,24 +3579,24 @@
         <v>25</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" ht="89.25" spans="1:14">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" ht="76.5" spans="1:14">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>37</v>
@@ -3581,10 +3611,10 @@
         <v>1474</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>42</v>
@@ -3593,7 +3623,7 @@
         <v>25</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="51" spans="1:14">
@@ -3601,22 +3631,22 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>39</v>
@@ -3625,10 +3655,10 @@
         <v>1468</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>42</v>
@@ -3637,30 +3667,30 @@
         <v>25</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" ht="63.75" spans="1:14">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" ht="51" spans="1:14">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>39</v>
@@ -3669,10 +3699,10 @@
         <v>1453</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>42</v>
@@ -3681,21 +3711,21 @@
         <v>25</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" ht="63.75" spans="1:14">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:14">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>58</v>
@@ -3704,7 +3734,7 @@
         <v>37</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>39</v>
@@ -3713,10 +3743,10 @@
         <v>1352</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>42</v>
@@ -3725,30 +3755,30 @@
         <v>25</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" ht="63.75" spans="1:14">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" ht="51" spans="1:14">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>39</v>
@@ -3757,10 +3787,10 @@
         <v>1300</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>42</v>
@@ -3769,30 +3799,30 @@
         <v>25</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" ht="76.5" spans="1:14">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" ht="63.75" spans="1:14">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>39</v>
@@ -3801,10 +3831,10 @@
         <v>1255</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>42</v>
@@ -3813,30 +3843,30 @@
         <v>25</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" ht="76.5" spans="1:14">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" ht="63.75" spans="1:14">
       <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -3845,10 +3875,10 @@
         <v>1280</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>42</v>
@@ -3857,42 +3887,42 @@
         <v>25</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" ht="51" spans="1:14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" ht="38.25" spans="1:14">
       <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I20" s="6">
         <v>1365</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>32</v>
@@ -3901,42 +3931,42 @@
         <v>25</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" ht="63.75" spans="1:14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" ht="38.25" spans="1:14">
       <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I21" s="6">
         <v>1365</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>32</v>
@@ -3945,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" ht="38.25" spans="1:14">
@@ -3953,104 +3983,104 @@
         <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" s="6">
         <v>1199</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" ht="51" spans="1:14">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="38.25" spans="1:14">
       <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I23" s="6">
         <v>1114</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" ht="114.75" spans="1:14">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" ht="102" spans="1:14">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>37</v>
@@ -4065,10 +4095,10 @@
         <v>1494</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>42</v>
@@ -4077,24 +4107,24 @@
         <v>25</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" ht="63.75" spans="1:14">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" ht="51" spans="1:14">
       <c r="A25" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>37</v>
@@ -4109,10 +4139,10 @@
         <v>1474</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>42</v>
@@ -4121,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" ht="102" spans="1:14">
@@ -4129,16 +4159,16 @@
         <v>14</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>37</v>
@@ -4153,10 +4183,10 @@
         <v>1450</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>42</v>
@@ -4164,25 +4194,25 @@
       <c r="M26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N26" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" ht="114.75" spans="1:14">
+      <c r="N26" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" ht="102" spans="1:14">
       <c r="A27" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>37</v>
@@ -4197,10 +4227,10 @@
         <v>1464</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>42</v>
@@ -4209,7 +4239,7 @@
         <v>25</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" ht="63.75" spans="1:14">
@@ -4217,43 +4247,43 @@
         <v>14</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I28" s="6">
         <v>1417</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" ht="63.75" spans="1:14">
@@ -4261,34 +4291,34 @@
         <v>14</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I29" s="6">
         <v>1368</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>24</v>
@@ -4297,27 +4327,27 @@
         <v>25</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="30" ht="51" spans="1:14">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" ht="38.25" spans="1:14">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>59</v>
@@ -4329,10 +4359,10 @@
         <v>1355</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>32</v>
@@ -4341,7 +4371,7 @@
         <v>25</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" ht="51" spans="1:14">
@@ -4349,22 +4379,22 @@
         <v>14</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>39</v>
@@ -4373,10 +4403,10 @@
         <v>1473</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>42</v>
@@ -4385,30 +4415,30 @@
         <v>25</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" ht="63.75" spans="1:14">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" ht="38.25" spans="1:14">
       <c r="A32" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>39</v>
@@ -4417,10 +4447,10 @@
         <v>1471</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>42</v>
@@ -4429,30 +4459,30 @@
         <v>25</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="33" ht="51" spans="1:14">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" ht="38.25" spans="1:14">
       <c r="A33" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>39</v>
@@ -4461,10 +4491,10 @@
         <v>1431</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>42</v>
@@ -4473,30 +4503,30 @@
         <v>25</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="34" ht="51" spans="1:14">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" ht="38.25" spans="1:14">
       <c r="A34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>39</v>
@@ -4505,10 +4535,10 @@
         <v>1412</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>42</v>
@@ -4517,7 +4547,7 @@
         <v>25</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" ht="63.75" spans="1:14">
@@ -4525,34 +4555,34 @@
         <v>14</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I35" s="6">
         <v>1365</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>24</v>
@@ -4561,7 +4591,7 @@
         <v>25</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:14">
@@ -4569,43 +4599,43 @@
         <v>14</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I36" s="6">
         <v>1108</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" ht="51" spans="1:14">
@@ -4613,43 +4643,43 @@
         <v>14</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I37" s="6">
         <v>1175</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" ht="51" spans="1:14">
@@ -4657,19 +4687,19 @@
         <v>14</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>59</v>
@@ -4681,10 +4711,10 @@
         <v>1331</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>32</v>
@@ -4693,30 +4723,30 @@
         <v>25</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="39" ht="63.75" spans="1:14">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" ht="51" spans="1:14">
       <c r="A39" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>21</v>
@@ -4725,19 +4755,19 @@
         <v>1331</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" ht="51" spans="1:14">
@@ -4745,34 +4775,34 @@
         <v>14</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I40" s="6">
         <v>1393</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>32</v>
@@ -4781,74 +4811,74 @@
         <v>25</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="41" ht="51" spans="1:14">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" ht="38.25" spans="1:14">
       <c r="A41" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I41" s="6">
         <v>1197</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="42" ht="51" spans="1:14">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" ht="38.25" spans="1:14">
       <c r="A42" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>21</v>
@@ -4857,42 +4887,42 @@
         <v>1376</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="43" ht="63.75" spans="1:14">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" ht="38.25" spans="1:14">
       <c r="A43" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>21</v>
@@ -4901,19 +4931,19 @@
         <v>1376</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" ht="51" spans="1:14">
@@ -4921,19 +4951,19 @@
         <v>14</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>38</v>
@@ -4945,10 +4975,10 @@
         <v>1400</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>32</v>
@@ -4957,306 +4987,306 @@
         <v>25</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" ht="51" spans="1:14">
       <c r="A45" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I45" s="6">
         <v>1407</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" ht="51" spans="1:14">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" ht="38.25" spans="1:14">
       <c r="A46" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I46" s="6">
         <v>1410</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="47" ht="51" spans="1:14">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="47" ht="38.25" spans="1:14">
       <c r="A47" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I47" s="6">
         <v>1456</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="48" ht="51" spans="1:14">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" ht="38.25" spans="1:14">
       <c r="A48" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I48" s="6">
         <v>1443</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" ht="63.75" spans="1:14">
       <c r="A49" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I49" s="6">
         <v>1426</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="50" ht="51" spans="1:14">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" ht="38.25" spans="1:14">
       <c r="A50" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I50" s="6">
         <v>1464</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="51" ht="51" spans="1:14">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" ht="38.25" spans="1:14">
       <c r="A51" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I51" s="6">
         <v>1422</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>24</v>
@@ -5265,42 +5295,42 @@
         <v>25</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="52" ht="89.25" spans="1:14">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52" ht="76.5" spans="1:14">
       <c r="A52" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I52" s="6">
         <v>1435</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>32</v>
@@ -5309,42 +5339,42 @@
         <v>25</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="53" ht="63.75" spans="1:14">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" ht="38.25" spans="1:14">
       <c r="A53" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I53" s="6">
         <v>1382</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>32</v>
@@ -5353,42 +5383,42 @@
         <v>25</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="54" ht="89.25" spans="1:14">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" ht="76.5" spans="1:14">
       <c r="A54" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I54" s="6">
         <v>1422</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>24</v>
@@ -5397,68 +5427,68 @@
         <v>25</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="55" ht="63.75" spans="1:14">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="55" ht="51" spans="1:14">
       <c r="A55" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I55" s="6">
         <v>1464</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" ht="51" spans="1:14">
       <c r="A56" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>37</v>
@@ -5473,10 +5503,10 @@
         <v>1495</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>42</v>
@@ -5485,426 +5515,426 @@
         <v>25</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="57" ht="63.75" spans="1:14">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="57" ht="51" spans="1:14">
       <c r="A57" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I57" s="6">
         <v>1424</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="58" ht="63.75" spans="1:14">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="58" ht="51" spans="1:14">
       <c r="A58" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I58" s="6">
         <v>1424</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" ht="51" spans="1:14">
       <c r="A59" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I59" s="6">
         <v>1423</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="60" ht="51" spans="1:14">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="60" ht="38.25" spans="1:14">
       <c r="A60" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I60" s="6">
         <v>1422</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="61" ht="89.25" spans="1:14">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="61" ht="76.5" spans="1:14">
       <c r="A61" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I61" s="6">
         <v>1416</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="62" ht="89.25" spans="1:14">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" ht="76.5" spans="1:14">
       <c r="A62" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I62" s="6">
         <v>1453</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N62" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" ht="51" spans="1:14">
       <c r="A63" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I63" s="6">
         <v>1430</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N63" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" ht="51" spans="1:14">
       <c r="A64" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I64" s="6">
         <v>1445</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="65" ht="63.75" spans="1:14">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="65" ht="51" spans="1:14">
       <c r="A65" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I65" s="6">
         <v>1420</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N65" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="66" ht="63.75" spans="1:14">
       <c r="A66" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>21</v>
@@ -5913,10 +5943,10 @@
         <v>1150</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L66" s="6" t="s">
         <v>32</v>
@@ -5925,30 +5955,30 @@
         <v>25</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="67" ht="76.5" spans="1:14">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="67" ht="63.75" spans="1:14">
       <c r="A67" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>21</v>
@@ -5957,10 +5987,10 @@
         <v>1350</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>24</v>
@@ -5969,74 +5999,74 @@
         <v>25</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="68" ht="63.75" spans="1:14">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="68" ht="51" spans="1:14">
       <c r="A68" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I68" s="6">
         <v>1415</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" ht="51" spans="1:14">
       <c r="A69" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>21</v>
@@ -6045,42 +6075,42 @@
         <v>1410</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="70" ht="63.75" spans="1:14">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="70" ht="51" spans="1:14">
       <c r="A70" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>21</v>
@@ -6089,10 +6119,10 @@
         <v>1357</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>32</v>
@@ -6101,86 +6131,86 @@
         <v>25</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="71" ht="63.75" spans="1:14">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="71" ht="51" spans="1:14">
       <c r="A71" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="H71" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="H71" s="13" t="s">
         <v>21</v>
       </c>
       <c r="I71" s="6">
         <v>1202</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N71" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" ht="51" spans="1:14">
       <c r="A72" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H72" s="14" t="s">
+      <c r="H72" s="13" t="s">
         <v>21</v>
       </c>
       <c r="I72" s="6">
         <v>1200</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L72" s="6" t="s">
         <v>32</v>
@@ -6189,42 +6219,42 @@
         <v>25</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="73" ht="51" spans="1:14">
       <c r="A73" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H73" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" s="13" t="s">
         <v>21</v>
       </c>
       <c r="I73" s="6">
         <v>1150</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>32</v>
@@ -6233,42 +6263,42 @@
         <v>55</v>
       </c>
       <c r="N73" s="11" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="74" ht="63.75" spans="1:14">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="74" ht="51" spans="1:14">
       <c r="A74" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>454</v>
+        <v>78</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>456</v>
       </c>
       <c r="I74" s="6">
         <v>1200</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>24</v>
@@ -6277,30 +6307,30 @@
         <v>55</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="75" ht="63.75" spans="1:14">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="75" ht="38.25" spans="1:14">
       <c r="A75" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>39</v>
@@ -6309,36 +6339,36 @@
         <v>1305</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N75" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="76" ht="51" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="76" ht="38.25" spans="1:14">
       <c r="A76" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>37</v>
@@ -6353,42 +6383,42 @@
         <v>1385</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N76" s="13" t="s">
-        <v>37</v>
+        <v>465</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="77" ht="51" spans="1:14">
       <c r="A77" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>39</v>
@@ -6397,124 +6427,124 @@
         <v>1350</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N77" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="78" ht="76.5" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="78" ht="51" spans="1:14">
       <c r="A78" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I78" s="6">
         <v>1350</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L78" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N78" s="11" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="79" ht="51" spans="1:14">
       <c r="A79" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I79" s="6">
         <v>1215</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N79" s="11" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="80" ht="63.75" spans="1:14">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="80" ht="51" spans="1:14">
       <c r="A80" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>37</v>
@@ -6529,42 +6559,42 @@
         <v>1381</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L80" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N80" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="81" ht="63.75" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="81" ht="51" spans="1:14">
       <c r="A81" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>39</v>
@@ -6573,42 +6603,42 @@
         <v>1300</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="L81" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N81" s="13" t="s">
-        <v>37</v>
+        <v>465</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="82" ht="51" spans="1:14">
       <c r="A82" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>39</v>
@@ -6617,42 +6647,42 @@
         <v>1150</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="L82" s="6" t="s">
         <v>42</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="N82" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="83" ht="63.75" spans="1:14">
+        <v>500</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="83" ht="38.25" spans="1:14">
       <c r="A83" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B83" s="15" t="s">
-        <v>494</v>
+        <v>460</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>502</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>21</v>
@@ -6661,171 +6691,171 @@
         <v>1180</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="L83" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N83" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="84" ht="63.75" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N83" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="84" ht="38.25" spans="1:14">
       <c r="A84" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I84" s="6">
         <v>1350</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="L84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N84" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="85" ht="63.75" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N84" s="12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="85" ht="51" spans="1:14">
       <c r="A85" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I85" s="6">
         <v>1150</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="L85" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="N85" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="N85" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="86" ht="38.25" spans="1:14">
+      <c r="A86" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="86" ht="51" spans="1:14">
-      <c r="A86" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>499</v>
-      </c>
       <c r="C86" s="5" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I86" s="6">
         <v>1200</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="L86" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N86" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="87" ht="51" spans="1:14">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="87" ht="38.25" spans="1:14">
       <c r="A87" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>59</v>
@@ -6837,230 +6867,230 @@
         <v>1225</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="L87" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N87" s="13" t="s">
-        <v>37</v>
+        <v>465</v>
+      </c>
+      <c r="N87" s="12" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="88" ht="63.75" spans="1:14">
       <c r="A88" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I88" s="6">
         <v>1180</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="L88" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="N88" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="89" ht="63.75" spans="1:14">
+        <v>465</v>
+      </c>
+      <c r="N88" s="12" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="89" ht="38.25" spans="1:14">
       <c r="A89" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I89" s="6">
         <v>1261</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N89" s="11" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="90" ht="63.75" spans="1:14">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="90" ht="51" spans="1:14">
       <c r="A90" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I90" s="6">
         <v>1025</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N90" s="11" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
     </row>
     <row r="91" ht="51" spans="1:14">
       <c r="A91" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I91" s="6">
         <v>1065</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="N91" s="11" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="92" ht="63.75" spans="1:14">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="92" ht="51" spans="1:14">
       <c r="A92" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I92" s="6">
         <v>1353</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="L92" s="6" t="s">
         <v>24</v>
@@ -7069,42 +7099,42 @@
         <v>25</v>
       </c>
       <c r="N92" s="11" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="93" ht="51" spans="1:14">
       <c r="A93" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I93" s="6">
         <v>1276</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="L93" s="6" t="s">
         <v>32</v>
@@ -7112,8 +7142,8 @@
       <c r="M93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N93" s="12" t="s">
-        <v>37</v>
+      <c r="N93" s="15" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1"/>
@@ -7198,6 +7228,18 @@
     <hyperlink ref="N5" r:id="rId78" display="https://openrouter.ai/openai/gpt-5.4"/>
     <hyperlink ref="N92" r:id="rId79" display="https://openrouter.ai/cohere/command-a"/>
     <hyperlink ref="N85" r:id="rId80" display="https://huggingface.co/itlwas/saiga_llama3_8b-Q4_K_M-GGUF" tooltip="https://huggingface.co/itlwas/saiga_llama3_8b-Q4_K_M-GGUF"/>
+    <hyperlink ref="N7" r:id="rId81" display="https://openai.com/ru-RU/index/gpt-5-3-instant/"/>
+    <hyperlink ref="N26" r:id="rId82" display="https://deepmind.google/models/gemini/pro/"/>
+    <hyperlink ref="N75" r:id="rId83" display="https://ya.ru/ai/aliceai"/>
+    <hyperlink ref="N76" r:id="rId84" display="https://ya.ru/ai/gpt"/>
+    <hyperlink ref="N77" r:id="rId85" display="https://fichi.ai/yandexgpt-5"/>
+    <hyperlink ref="N80" r:id="rId86" display="https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-max"/>
+    <hyperlink ref="N81" r:id="rId87" display="https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-pro"/>
+    <hyperlink ref="N82" r:id="rId88" display="https://developers.sber.ru/docs/ru/gigachat/models/gigachat-2-lite"/>
+    <hyperlink ref="N83" r:id="rId89" display="https://habr.com/ru/companies/tbank/articles/928956/"/>
+    <hyperlink ref="N84" r:id="rId90" display="https://denciaopin.com/articles/saiga-family/"/>
+    <hyperlink ref="N87" r:id="rId91" display="https://huggingface.co/tripolskypetr/Vikhr-Nemo-12B-Instruct"/>
+    <hyperlink ref="N88" r:id="rId92" display="https://huggingface.co/QuantFactory/Vikhr-Llama3.1-8B-Instruct-R-21-09-24-GGUF"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
